--- a/artfynd/A 43541-2023 artfynd.xlsx
+++ b/artfynd/A 43541-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 43541-2023 artfynd.xlsx
+++ b/artfynd/A 43541-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>87490886</v>
+        <v>87487080</v>
       </c>
       <c r="B4" t="n">
-        <v>78596</v>
+        <v>89410</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>460020.8773744333</v>
+        <v>459983.0108737128</v>
       </c>
       <c r="R4" t="n">
-        <v>7077520.990955303</v>
+        <v>7077533.838620799</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -999,22 +999,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Tove Lönneborg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tore Dahlberg, Karl Soler Kinnerbäck, Tove Lönneborg, Vera Ranow</t>
+          <t>Tove Lönneborg, Tore Dahlberg, Karl Soler Kinnerbäck, Elin Lönnberg, Vera Ranow</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>87487080</v>
+        <v>87490917</v>
       </c>
       <c r="B5" t="n">
-        <v>89410</v>
+        <v>77506</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459983.0108737128</v>
+        <v>460020.8773744333</v>
       </c>
       <c r="R5" t="n">
-        <v>7077533.838620799</v>
+        <v>7077520.990955303</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1111,22 +1111,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Tove Lönneborg</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Tove Lönneborg, Tore Dahlberg, Karl Soler Kinnerbäck, Elin Lönnberg, Vera Ranow</t>
+          <t>Tore Dahlberg, Karl Soler Kinnerbäck, Tove Lönneborg, Vera Ranow</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>87490917</v>
+        <v>87490908</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
+        <v>78533</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,25 +1135,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>229748</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>460020.8773744333</v>
+        <v>460030.021876041</v>
       </c>
       <c r="R6" t="n">
-        <v>7077520.990955303</v>
+        <v>7077509.833818755</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>87490908</v>
+        <v>112769836</v>
       </c>
       <c r="B7" t="n">
-        <v>78533</v>
+        <v>77981</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,41 +1247,44 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229748</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Höktjärnbäcken, Jmt</t>
+          <t>Svedbodarna Skärvången, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>460030.021876041</v>
+        <v>460161</v>
       </c>
       <c r="R7" t="n">
-        <v>7077509.833818755</v>
+        <v>7077214</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,22 +1308,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2020-08-09</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2020-08-09</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-16</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1329,28 +1327,29 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Tore Dahlberg, Karl Soler Kinnerbäck, Tove Lönneborg, Vera Ranow</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112769836</v>
+        <v>112769815</v>
       </c>
       <c r="B8" t="n">
-        <v>77981</v>
+        <v>56746</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,37 +1362,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Svedbodarna Skärvången, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>460161</v>
+        <v>460116</v>
       </c>
       <c r="R8" t="n">
-        <v>7077214</v>
+        <v>7077318</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1430,7 +1426,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1439,7 +1435,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1458,7 +1453,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112769815</v>
+        <v>112769808</v>
       </c>
       <c r="B9" t="n">
         <v>56746</v>
@@ -1498,10 +1493,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>460116</v>
+        <v>459886</v>
       </c>
       <c r="R9" t="n">
-        <v>7077318</v>
+        <v>7077602</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1538,7 +1533,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1565,7 +1560,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112769808</v>
+        <v>112769810</v>
       </c>
       <c r="B10" t="n">
         <v>56746</v>
@@ -1605,10 +1600,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>459886</v>
+        <v>459659</v>
       </c>
       <c r="R10" t="n">
-        <v>7077602</v>
+        <v>7077628</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1645,7 +1640,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1672,10 +1667,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112769810</v>
+        <v>112769830</v>
       </c>
       <c r="B11" t="n">
-        <v>56746</v>
+        <v>77981</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1688,34 +1683,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Svedbodarna Skärvången, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>459659</v>
+        <v>460066</v>
       </c>
       <c r="R11" t="n">
-        <v>7077628</v>
+        <v>7077384</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1752,7 +1750,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1761,6 +1759,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1779,7 +1778,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112769830</v>
+        <v>112769829</v>
       </c>
       <c r="B12" t="n">
         <v>77981</v>
@@ -1822,10 +1821,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>460066</v>
+        <v>460154</v>
       </c>
       <c r="R12" t="n">
-        <v>7077384</v>
+        <v>7077489</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1890,10 +1889,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112769829</v>
+        <v>112769801</v>
       </c>
       <c r="B13" t="n">
-        <v>77981</v>
+        <v>90583</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1902,41 +1901,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Svedbodarna Skärvången, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>460154</v>
+        <v>459981</v>
       </c>
       <c r="R13" t="n">
-        <v>7077489</v>
+        <v>7077408</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1971,18 +1967,12 @@
           <t>2023-10-16</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>rikligt</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2001,10 +1991,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112769801</v>
+        <v>112769806</v>
       </c>
       <c r="B14" t="n">
-        <v>90583</v>
+        <v>56746</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2013,25 +2003,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2041,10 +2031,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>459981</v>
+        <v>460220</v>
       </c>
       <c r="R14" t="n">
-        <v>7077408</v>
+        <v>7077367</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2077,6 +2067,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-10-16</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2103,10 +2098,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112769806</v>
+        <v>112769802</v>
       </c>
       <c r="B15" t="n">
-        <v>56746</v>
+        <v>90583</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2115,25 +2110,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2143,10 +2138,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>460220</v>
+        <v>460157</v>
       </c>
       <c r="R15" t="n">
-        <v>7077367</v>
+        <v>7077216</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2179,11 +2174,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-10-16</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2210,10 +2200,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112769802</v>
+        <v>112769820</v>
       </c>
       <c r="B16" t="n">
-        <v>90583</v>
+        <v>89897</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2222,25 +2212,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2250,10 +2240,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>460157</v>
+        <v>460152</v>
       </c>
       <c r="R16" t="n">
-        <v>7077216</v>
+        <v>7077440</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2312,10 +2302,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112769820</v>
+        <v>112769837</v>
       </c>
       <c r="B17" t="n">
-        <v>89897</v>
+        <v>86197</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2328,21 +2318,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>510</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2352,10 +2342,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>460152</v>
+        <v>459965</v>
       </c>
       <c r="R17" t="n">
-        <v>7077440</v>
+        <v>7077442</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2414,10 +2404,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>112769837</v>
+        <v>112769814</v>
       </c>
       <c r="B18" t="n">
-        <v>86197</v>
+        <v>56746</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2430,21 +2420,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2454,10 +2444,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>459965</v>
+        <v>460015</v>
       </c>
       <c r="R18" t="n">
-        <v>7077442</v>
+        <v>7077372</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2490,6 +2480,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-10-16</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2516,10 +2511,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112769814</v>
+        <v>112769835</v>
       </c>
       <c r="B19" t="n">
-        <v>56746</v>
+        <v>77981</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2532,34 +2527,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Svedbodarna Skärvången, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>460015</v>
+        <v>460150</v>
       </c>
       <c r="R19" t="n">
-        <v>7077372</v>
+        <v>7077286</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2596,7 +2594,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2605,6 +2603,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2623,7 +2622,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>112769835</v>
+        <v>112769827</v>
       </c>
       <c r="B20" t="n">
         <v>77981</v>
@@ -2666,10 +2665,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>460150</v>
+        <v>460299</v>
       </c>
       <c r="R20" t="n">
-        <v>7077286</v>
+        <v>7077377</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2734,10 +2733,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112769827</v>
+        <v>112769805</v>
       </c>
       <c r="B21" t="n">
-        <v>77981</v>
+        <v>56746</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2750,37 +2749,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Svedbodarna Skärvången, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>460299</v>
+        <v>460268</v>
       </c>
       <c r="R21" t="n">
-        <v>7077377</v>
+        <v>7077413</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2817,7 +2813,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2826,7 +2822,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2845,7 +2840,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112769805</v>
+        <v>112769813</v>
       </c>
       <c r="B22" t="n">
         <v>56746</v>
@@ -2885,10 +2880,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>460268</v>
+        <v>459963</v>
       </c>
       <c r="R22" t="n">
-        <v>7077413</v>
+        <v>7077437</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2925,7 +2920,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2952,7 +2947,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>112769813</v>
+        <v>112769804</v>
       </c>
       <c r="B23" t="n">
         <v>56746</v>
@@ -2992,10 +2987,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>459963</v>
+        <v>460242</v>
       </c>
       <c r="R23" t="n">
-        <v>7077437</v>
+        <v>7077229</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3059,7 +3054,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>112769804</v>
+        <v>112769816</v>
       </c>
       <c r="B24" t="n">
         <v>56746</v>
@@ -3099,10 +3094,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>460242</v>
+        <v>460123</v>
       </c>
       <c r="R24" t="n">
-        <v>7077229</v>
+        <v>7077317</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3139,7 +3134,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3166,10 +3161,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>112769816</v>
+        <v>112769799</v>
       </c>
       <c r="B25" t="n">
-        <v>56746</v>
+        <v>90583</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3178,25 +3173,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3206,10 +3201,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>460123</v>
+        <v>460132</v>
       </c>
       <c r="R25" t="n">
-        <v>7077317</v>
+        <v>7077512</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3242,11 +3237,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2023-10-16</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3273,10 +3263,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>112769799</v>
+        <v>112769803</v>
       </c>
       <c r="B26" t="n">
-        <v>90583</v>
+        <v>56746</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3285,25 +3275,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3313,10 +3303,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>460132</v>
+        <v>460371</v>
       </c>
       <c r="R26" t="n">
-        <v>7077512</v>
+        <v>7077335</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3349,6 +3339,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2023-10-16</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3375,10 +3370,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>112769803</v>
+        <v>112769821</v>
       </c>
       <c r="B27" t="n">
-        <v>56746</v>
+        <v>89919</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3391,21 +3386,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3415,10 +3410,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>460371</v>
+        <v>460268</v>
       </c>
       <c r="R27" t="n">
-        <v>7077335</v>
+        <v>7077450</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3451,11 +3446,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2023-10-16</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3482,7 +3472,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>112769821</v>
+        <v>112769822</v>
       </c>
       <c r="B28" t="n">
         <v>89919</v>
@@ -3522,10 +3512,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>460268</v>
+        <v>460082</v>
       </c>
       <c r="R28" t="n">
-        <v>7077450</v>
+        <v>7077490</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3584,10 +3574,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>112769822</v>
+        <v>112769831</v>
       </c>
       <c r="B29" t="n">
-        <v>89919</v>
+        <v>77981</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3600,34 +3590,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Svedbodarna Skärvången, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>460082</v>
+        <v>459774</v>
       </c>
       <c r="R29" t="n">
-        <v>7077490</v>
+        <v>7077615</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3662,12 +3655,18 @@
           <t>2023-10-16</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>rikligt</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3686,7 +3685,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>112769831</v>
+        <v>112769834</v>
       </c>
       <c r="B30" t="n">
         <v>77981</v>
@@ -3729,10 +3728,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>459774</v>
+        <v>460026</v>
       </c>
       <c r="R30" t="n">
-        <v>7077615</v>
+        <v>7077354</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3797,10 +3796,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>112769834</v>
+        <v>112769812</v>
       </c>
       <c r="B31" t="n">
-        <v>77981</v>
+        <v>56746</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3813,37 +3812,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Svedbodarna Skärvången, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>460026</v>
+        <v>459702</v>
       </c>
       <c r="R31" t="n">
-        <v>7077354</v>
+        <v>7077612</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3880,7 +3876,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3889,7 +3885,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3908,10 +3903,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>112769812</v>
+        <v>112769825</v>
       </c>
       <c r="B32" t="n">
-        <v>56746</v>
+        <v>89919</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3924,21 +3919,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3948,10 +3943,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>459702</v>
+        <v>459944</v>
       </c>
       <c r="R32" t="n">
-        <v>7077612</v>
+        <v>7077567</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3984,11 +3979,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2023-10-16</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4015,7 +4005,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>112769825</v>
+        <v>112769823</v>
       </c>
       <c r="B33" t="n">
         <v>89919</v>
@@ -4055,10 +4045,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>459944</v>
+        <v>459998</v>
       </c>
       <c r="R33" t="n">
-        <v>7077567</v>
+        <v>7077493</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4117,10 +4107,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>112769823</v>
+        <v>112769833</v>
       </c>
       <c r="B34" t="n">
-        <v>89919</v>
+        <v>77981</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4133,34 +4123,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Svedbodarna Skärvången, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>459998</v>
+        <v>459985</v>
       </c>
       <c r="R34" t="n">
-        <v>7077493</v>
+        <v>7077407</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4195,12 +4188,18 @@
           <t>2023-10-16</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>rikligt</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4219,10 +4218,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>112769833</v>
+        <v>112769824</v>
       </c>
       <c r="B35" t="n">
-        <v>77981</v>
+        <v>89919</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4235,37 +4234,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Svedbodarna Skärvången, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>459985</v>
+        <v>459967</v>
       </c>
       <c r="R35" t="n">
-        <v>7077407</v>
+        <v>7077537</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4300,18 +4296,12 @@
           <t>2023-10-16</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>rikligt</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4330,10 +4320,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>112769824</v>
+        <v>112769800</v>
       </c>
       <c r="B36" t="n">
-        <v>89919</v>
+        <v>90583</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4342,25 +4332,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4370,10 +4360,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>459967</v>
+        <v>459756</v>
       </c>
       <c r="R36" t="n">
-        <v>7077537</v>
+        <v>7077610</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4432,10 +4422,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>112769800</v>
+        <v>112769818</v>
       </c>
       <c r="B37" t="n">
-        <v>90583</v>
+        <v>56746</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4444,25 +4434,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4472,10 +4462,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>459756</v>
+        <v>460180</v>
       </c>
       <c r="R37" t="n">
-        <v>7077610</v>
+        <v>7077236</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4508,6 +4498,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2023-10-16</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4534,7 +4529,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>112769818</v>
+        <v>112769809</v>
       </c>
       <c r="B38" t="n">
         <v>56746</v>
@@ -4574,10 +4569,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>460180</v>
+        <v>459659</v>
       </c>
       <c r="R38" t="n">
-        <v>7077236</v>
+        <v>7077629</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4641,10 +4636,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>112769809</v>
+        <v>112769798</v>
       </c>
       <c r="B39" t="n">
-        <v>56746</v>
+        <v>90583</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4653,25 +4648,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4681,10 +4676,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>459659</v>
+        <v>460168</v>
       </c>
       <c r="R39" t="n">
-        <v>7077629</v>
+        <v>7077479</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4719,11 +4714,6 @@
           <t>2023-10-16</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -4745,108 +4735,6 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>112769798</v>
-      </c>
-      <c r="B40" t="n">
-        <v>90583</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>3298</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Trådticka</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>Svedbodarna Skärvången, Jmt</t>
-        </is>
-      </c>
-      <c r="Q40" t="n">
-        <v>460168</v>
-      </c>
-      <c r="R40" t="n">
-        <v>7077479</v>
-      </c>
-      <c r="S40" t="n">
-        <v>10</v>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>2023-10-16</t>
-        </is>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>2023-10-16</t>
-        </is>
-      </c>
-      <c r="AD40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT40" t="inlineStr"/>
-      <c r="AW40" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43541-2023 artfynd.xlsx
+++ b/artfynd/A 43541-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AY41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112769836</v>
+        <v>87490885</v>
       </c>
       <c r="B7" t="n">
-        <v>77981</v>
+        <v>78596</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,44 +1247,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svedbodarna Skärvången, Jmt</t>
+          <t>Höktjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>460161</v>
+        <v>460058.8171434411</v>
       </c>
       <c r="R7" t="n">
-        <v>7077214</v>
+        <v>7077513.883995097</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1308,17 +1305,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2020-08-09</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>rikligt</t>
+          <t>2020-08-09</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,29 +1329,28 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Tore Dahlberg, Karl Soler Kinnerbäck, Tove Lönneborg, Vera Ranow</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112769815</v>
+        <v>112769836</v>
       </c>
       <c r="B8" t="n">
-        <v>56746</v>
+        <v>77981</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1362,34 +1363,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Svedbodarna Skärvången, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>460116</v>
+        <v>460161</v>
       </c>
       <c r="R8" t="n">
-        <v>7077318</v>
+        <v>7077214</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1426,7 +1430,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1435,6 +1439,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1453,7 +1458,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112769808</v>
+        <v>112769815</v>
       </c>
       <c r="B9" t="n">
         <v>56746</v>
@@ -1493,10 +1498,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459886</v>
+        <v>460116</v>
       </c>
       <c r="R9" t="n">
-        <v>7077602</v>
+        <v>7077318</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1533,7 +1538,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1560,7 +1565,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112769810</v>
+        <v>112769808</v>
       </c>
       <c r="B10" t="n">
         <v>56746</v>
@@ -1600,10 +1605,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>459659</v>
+        <v>459886</v>
       </c>
       <c r="R10" t="n">
-        <v>7077628</v>
+        <v>7077602</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1640,7 +1645,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1667,10 +1672,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112769830</v>
+        <v>112769810</v>
       </c>
       <c r="B11" t="n">
-        <v>77981</v>
+        <v>56746</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1683,37 +1688,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Svedbodarna Skärvången, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>460066</v>
+        <v>459659</v>
       </c>
       <c r="R11" t="n">
-        <v>7077384</v>
+        <v>7077628</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1750,7 +1752,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1759,7 +1761,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1778,7 +1779,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112769829</v>
+        <v>112769830</v>
       </c>
       <c r="B12" t="n">
         <v>77981</v>
@@ -1821,10 +1822,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>460154</v>
+        <v>460066</v>
       </c>
       <c r="R12" t="n">
-        <v>7077489</v>
+        <v>7077384</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1889,10 +1890,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112769801</v>
+        <v>112769829</v>
       </c>
       <c r="B13" t="n">
-        <v>90583</v>
+        <v>77981</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1901,38 +1902,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Svedbodarna Skärvången, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>459981</v>
+        <v>460154</v>
       </c>
       <c r="R13" t="n">
-        <v>7077408</v>
+        <v>7077489</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1967,12 +1971,18 @@
           <t>2023-10-16</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>rikligt</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1991,10 +2001,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112769806</v>
+        <v>112769801</v>
       </c>
       <c r="B14" t="n">
-        <v>56746</v>
+        <v>90583</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2003,25 +2013,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2031,10 +2041,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>460220</v>
+        <v>459981</v>
       </c>
       <c r="R14" t="n">
-        <v>7077367</v>
+        <v>7077408</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2067,11 +2077,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-10-16</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2098,10 +2103,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112769802</v>
+        <v>112769806</v>
       </c>
       <c r="B15" t="n">
-        <v>90583</v>
+        <v>56746</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2110,25 +2115,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2138,10 +2143,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>460157</v>
+        <v>460220</v>
       </c>
       <c r="R15" t="n">
-        <v>7077216</v>
+        <v>7077367</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2174,6 +2179,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-10-16</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2200,10 +2210,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112769820</v>
+        <v>112769802</v>
       </c>
       <c r="B16" t="n">
-        <v>89897</v>
+        <v>90583</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2212,25 +2222,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2240,10 +2250,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>460152</v>
+        <v>460157</v>
       </c>
       <c r="R16" t="n">
-        <v>7077440</v>
+        <v>7077216</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2302,10 +2312,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112769837</v>
+        <v>112769820</v>
       </c>
       <c r="B17" t="n">
-        <v>86197</v>
+        <v>89897</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2318,21 +2328,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>510</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2342,10 +2352,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>459965</v>
+        <v>460152</v>
       </c>
       <c r="R17" t="n">
-        <v>7077442</v>
+        <v>7077440</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2404,10 +2414,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>112769814</v>
+        <v>112769837</v>
       </c>
       <c r="B18" t="n">
-        <v>56746</v>
+        <v>86197</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2420,21 +2430,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2444,10 +2454,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>460015</v>
+        <v>459965</v>
       </c>
       <c r="R18" t="n">
-        <v>7077372</v>
+        <v>7077442</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2480,11 +2490,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-10-16</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2511,10 +2516,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112769835</v>
+        <v>112769814</v>
       </c>
       <c r="B19" t="n">
-        <v>77981</v>
+        <v>56746</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2527,37 +2532,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Svedbodarna Skärvången, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>460150</v>
+        <v>460015</v>
       </c>
       <c r="R19" t="n">
-        <v>7077286</v>
+        <v>7077372</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2594,7 +2596,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2603,7 +2605,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2622,7 +2623,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>112769827</v>
+        <v>112769835</v>
       </c>
       <c r="B20" t="n">
         <v>77981</v>
@@ -2665,10 +2666,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>460299</v>
+        <v>460150</v>
       </c>
       <c r="R20" t="n">
-        <v>7077377</v>
+        <v>7077286</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2733,10 +2734,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112769805</v>
+        <v>112769827</v>
       </c>
       <c r="B21" t="n">
-        <v>56746</v>
+        <v>77981</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2749,34 +2750,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Svedbodarna Skärvången, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>460268</v>
+        <v>460299</v>
       </c>
       <c r="R21" t="n">
-        <v>7077413</v>
+        <v>7077377</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2813,7 +2817,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2822,6 +2826,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2840,7 +2845,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112769813</v>
+        <v>112769805</v>
       </c>
       <c r="B22" t="n">
         <v>56746</v>
@@ -2880,10 +2885,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>459963</v>
+        <v>460268</v>
       </c>
       <c r="R22" t="n">
-        <v>7077437</v>
+        <v>7077413</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2920,7 +2925,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2947,7 +2952,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>112769804</v>
+        <v>112769813</v>
       </c>
       <c r="B23" t="n">
         <v>56746</v>
@@ -2987,10 +2992,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>460242</v>
+        <v>459963</v>
       </c>
       <c r="R23" t="n">
-        <v>7077229</v>
+        <v>7077437</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3054,7 +3059,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>112769816</v>
+        <v>112769804</v>
       </c>
       <c r="B24" t="n">
         <v>56746</v>
@@ -3094,10 +3099,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>460123</v>
+        <v>460242</v>
       </c>
       <c r="R24" t="n">
-        <v>7077317</v>
+        <v>7077229</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3134,7 +3139,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3161,10 +3166,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>112769799</v>
+        <v>112769816</v>
       </c>
       <c r="B25" t="n">
-        <v>90583</v>
+        <v>56746</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3173,25 +3178,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3201,10 +3206,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>460132</v>
+        <v>460123</v>
       </c>
       <c r="R25" t="n">
-        <v>7077512</v>
+        <v>7077317</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3237,6 +3242,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2023-10-16</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3263,10 +3273,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>112769803</v>
+        <v>112769799</v>
       </c>
       <c r="B26" t="n">
-        <v>56746</v>
+        <v>90583</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3275,25 +3285,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3303,10 +3313,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>460371</v>
+        <v>460132</v>
       </c>
       <c r="R26" t="n">
-        <v>7077335</v>
+        <v>7077512</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3339,11 +3349,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2023-10-16</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3370,10 +3375,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>112769821</v>
+        <v>112769803</v>
       </c>
       <c r="B27" t="n">
-        <v>89919</v>
+        <v>56746</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3386,21 +3391,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3410,10 +3415,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>460268</v>
+        <v>460371</v>
       </c>
       <c r="R27" t="n">
-        <v>7077450</v>
+        <v>7077335</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3446,6 +3451,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2023-10-16</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3472,7 +3482,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>112769822</v>
+        <v>112769821</v>
       </c>
       <c r="B28" t="n">
         <v>89919</v>
@@ -3512,10 +3522,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>460082</v>
+        <v>460268</v>
       </c>
       <c r="R28" t="n">
-        <v>7077490</v>
+        <v>7077450</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3574,10 +3584,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>112769831</v>
+        <v>112769822</v>
       </c>
       <c r="B29" t="n">
-        <v>77981</v>
+        <v>89919</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3590,37 +3600,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Svedbodarna Skärvången, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>459774</v>
+        <v>460082</v>
       </c>
       <c r="R29" t="n">
-        <v>7077615</v>
+        <v>7077490</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3655,18 +3662,12 @@
           <t>2023-10-16</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>rikligt</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3685,7 +3686,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>112769834</v>
+        <v>112769831</v>
       </c>
       <c r="B30" t="n">
         <v>77981</v>
@@ -3728,10 +3729,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>460026</v>
+        <v>459774</v>
       </c>
       <c r="R30" t="n">
-        <v>7077354</v>
+        <v>7077615</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3796,10 +3797,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>112769812</v>
+        <v>112769834</v>
       </c>
       <c r="B31" t="n">
-        <v>56746</v>
+        <v>77981</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3812,34 +3813,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Svedbodarna Skärvången, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>459702</v>
+        <v>460026</v>
       </c>
       <c r="R31" t="n">
-        <v>7077612</v>
+        <v>7077354</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3876,7 +3880,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3885,6 +3889,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3903,10 +3908,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>112769825</v>
+        <v>112769812</v>
       </c>
       <c r="B32" t="n">
-        <v>89919</v>
+        <v>56746</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3919,21 +3924,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3943,10 +3948,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>459944</v>
+        <v>459702</v>
       </c>
       <c r="R32" t="n">
-        <v>7077567</v>
+        <v>7077612</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3979,6 +3984,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2023-10-16</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4005,7 +4015,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>112769823</v>
+        <v>112769825</v>
       </c>
       <c r="B33" t="n">
         <v>89919</v>
@@ -4045,10 +4055,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>459998</v>
+        <v>459944</v>
       </c>
       <c r="R33" t="n">
-        <v>7077493</v>
+        <v>7077567</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4107,10 +4117,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>112769833</v>
+        <v>112769823</v>
       </c>
       <c r="B34" t="n">
-        <v>77981</v>
+        <v>89919</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4123,37 +4133,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Svedbodarna Skärvången, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>459985</v>
+        <v>459998</v>
       </c>
       <c r="R34" t="n">
-        <v>7077407</v>
+        <v>7077493</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4188,18 +4195,12 @@
           <t>2023-10-16</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>rikligt</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4218,10 +4219,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>112769824</v>
+        <v>112769833</v>
       </c>
       <c r="B35" t="n">
-        <v>89919</v>
+        <v>77981</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4234,34 +4235,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Svedbodarna Skärvången, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>459967</v>
+        <v>459985</v>
       </c>
       <c r="R35" t="n">
-        <v>7077537</v>
+        <v>7077407</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4296,12 +4300,18 @@
           <t>2023-10-16</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>rikligt</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4320,10 +4330,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>112769800</v>
+        <v>112769824</v>
       </c>
       <c r="B36" t="n">
-        <v>90583</v>
+        <v>89919</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4332,25 +4342,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4360,10 +4370,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>459756</v>
+        <v>459967</v>
       </c>
       <c r="R36" t="n">
-        <v>7077610</v>
+        <v>7077537</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4422,10 +4432,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>112769818</v>
+        <v>112769832</v>
       </c>
       <c r="B37" t="n">
-        <v>56746</v>
+        <v>77981</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4438,34 +4448,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Svedbodarna Skärvången, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>460180</v>
+        <v>459796</v>
       </c>
       <c r="R37" t="n">
-        <v>7077236</v>
+        <v>7077506</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4502,7 +4515,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4511,6 +4524,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4529,10 +4543,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>112769809</v>
+        <v>112769800</v>
       </c>
       <c r="B38" t="n">
-        <v>56746</v>
+        <v>90583</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4541,25 +4555,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4569,10 +4583,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>459659</v>
+        <v>459756</v>
       </c>
       <c r="R38" t="n">
-        <v>7077629</v>
+        <v>7077610</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4605,11 +4619,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2023-10-16</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4636,10 +4645,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>112769798</v>
+        <v>112769818</v>
       </c>
       <c r="B39" t="n">
-        <v>90583</v>
+        <v>56746</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4648,25 +4657,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4676,10 +4685,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>460168</v>
+        <v>460180</v>
       </c>
       <c r="R39" t="n">
-        <v>7077479</v>
+        <v>7077236</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4714,6 +4723,11 @@
           <t>2023-10-16</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -4735,6 +4749,215 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>112769809</v>
+      </c>
+      <c r="B40" t="n">
+        <v>56746</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Svedbodarna Skärvången, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>459659</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7077629</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2023-10-16</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2023-10-16</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>112769798</v>
+      </c>
+      <c r="B41" t="n">
+        <v>90583</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Svedbodarna Skärvången, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>460168</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7077479</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2023-10-16</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2023-10-16</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43541-2023 artfynd.xlsx
+++ b/artfynd/A 43541-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AY44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>87490916</v>
+        <v>112769837</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Höktjärnbäcken, Jmt</t>
+          <t>Svedbodarna Skärvången, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>460035.0539041042</v>
+        <v>459965</v>
       </c>
       <c r="R2" t="n">
-        <v>7077523.018773211</v>
+        <v>7077442</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-08-09</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-08-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,49 +760,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tore Dahlberg, Karl Soler Kinnerbäck, Tove Lönneborg, Vera Ranow</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>87490887</v>
+        <v>87490895</v>
       </c>
       <c r="B3" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>460020.8661383741</v>
+        <v>460041</v>
       </c>
       <c r="R3" t="n">
-        <v>7077520.107835399</v>
+        <v>7077529</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -860,19 +840,9 @@
           <t>2020-08-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-08-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,22 +862,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tore Dahlberg, Karl Soler Kinnerbäck, Tove Lönneborg, Vera Ranow</t>
+          <t>Vera Ranow, Tore Dahlberg, Karl Soler Kinnerbäck, Tove Lönneborg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>87487080</v>
+        <v>87490896</v>
       </c>
       <c r="B4" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459983.0108737128</v>
+        <v>460037</v>
       </c>
       <c r="R4" t="n">
-        <v>7077533.838620799</v>
+        <v>7077528</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -972,19 +937,9 @@
           <t>2020-08-09</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-08-09</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,27 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tove Lönneborg</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tove Lönneborg, Tore Dahlberg, Karl Soler Kinnerbäck, Elin Lönnberg, Vera Ranow</t>
+          <t>Tore Dahlberg, Karl Soler Kinnerbäck, Tove Lönneborg, Vera Ranow</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>87490917</v>
+        <v>112769820</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,37 +977,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Höktjärnbäcken, Jmt</t>
+          <t>Svedbodarna Skärvången, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>460020.8773744333</v>
+        <v>460152</v>
       </c>
       <c r="R5" t="n">
-        <v>7077520.990955303</v>
+        <v>7077440</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,22 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-08-09</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-08-09</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,49 +1051,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Tore Dahlberg, Karl Soler Kinnerbäck, Tove Lönneborg, Vera Ranow</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>87490908</v>
+        <v>87490875</v>
       </c>
       <c r="B6" t="n">
-        <v>78533</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229748</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>460030.021876041</v>
+        <v>460041</v>
       </c>
       <c r="R6" t="n">
-        <v>7077509.833818755</v>
+        <v>7077529</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1196,19 +1131,9 @@
           <t>2020-08-09</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-08-09</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>87490885</v>
+        <v>87490876</v>
       </c>
       <c r="B7" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>460058.8171434411</v>
+        <v>460040</v>
       </c>
       <c r="R7" t="n">
-        <v>7077513.883995097</v>
+        <v>7077538</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1308,19 +1228,9 @@
           <t>2020-08-09</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2020-08-09</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,56 +1257,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112769836</v>
+        <v>87485661</v>
       </c>
       <c r="B8" t="n">
-        <v>77981</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svedbodarna Skärvången, Jmt</t>
+          <t>Höktjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>460161</v>
+        <v>459793</v>
       </c>
       <c r="R8" t="n">
-        <v>7077214</v>
+        <v>7077725</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1420,17 +1322,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2020-08-09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>rikligt</t>
+          <t>2020-08-09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1439,56 +1336,50 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Vera Ranow</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Vera Ranow, Tore Dahlberg, Karl Soler Kinnerbäck, Tove Lönneborg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112769815</v>
+        <v>112769798</v>
       </c>
       <c r="B9" t="n">
-        <v>56746</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1498,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>460116</v>
+        <v>460168</v>
       </c>
       <c r="R9" t="n">
-        <v>7077318</v>
+        <v>7077479</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1534,11 +1425,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-10-16</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1565,37 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112769808</v>
+        <v>112769799</v>
       </c>
       <c r="B10" t="n">
-        <v>56746</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1605,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>459886</v>
+        <v>460132</v>
       </c>
       <c r="R10" t="n">
-        <v>7077602</v>
+        <v>7077511</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,11 +1522,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-10-16</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1672,37 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112769810</v>
+        <v>112769800</v>
       </c>
       <c r="B11" t="n">
-        <v>56746</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1712,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>459659</v>
+        <v>459756</v>
       </c>
       <c r="R11" t="n">
-        <v>7077628</v>
+        <v>7077609</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1748,11 +1619,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-10-16</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1779,53 +1645,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112769830</v>
+        <v>112769801</v>
       </c>
       <c r="B12" t="n">
-        <v>77981</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Svedbodarna Skärvången, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>460066</v>
+        <v>459980</v>
       </c>
       <c r="R12" t="n">
-        <v>7077384</v>
+        <v>7077409</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1860,18 +1718,12 @@
           <t>2023-10-16</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>rikligt</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1890,53 +1742,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112769829</v>
+        <v>112769802</v>
       </c>
       <c r="B13" t="n">
-        <v>77981</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Svedbodarna Skärvången, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>460154</v>
+        <v>460157</v>
       </c>
       <c r="R13" t="n">
-        <v>7077489</v>
+        <v>7077216</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1971,18 +1815,12 @@
           <t>2023-10-16</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>rikligt</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2001,53 +1839,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112769801</v>
+        <v>87487081</v>
       </c>
       <c r="B14" t="n">
-        <v>90583</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Svedbodarna Skärvången, Jmt</t>
+          <t>Höktjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>459981</v>
+        <v>459817</v>
       </c>
       <c r="R14" t="n">
-        <v>7077408</v>
+        <v>7077702</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2071,12 +1904,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2020-08-09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2020-08-09</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2091,65 +1924,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Tove Lönneborg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Tove Lönneborg, Tore Dahlberg, Karl Soler Kinnerbäck, Elin Lönnberg, Vera Ranow</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112769806</v>
+        <v>87490916</v>
       </c>
       <c r="B15" t="n">
-        <v>56746</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Svedbodarna Skärvången, Jmt</t>
+          <t>Höktjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>460220</v>
+        <v>460035</v>
       </c>
       <c r="R15" t="n">
-        <v>7077367</v>
+        <v>7077523</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2173,17 +2001,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2020-08-09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2020-08-09</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2198,65 +2021,60 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Tore Dahlberg, Karl Soler Kinnerbäck, Tove Lönneborg, Vera Ranow</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112769802</v>
+        <v>87490917</v>
       </c>
       <c r="B16" t="n">
-        <v>90583</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Svedbodarna Skärvången, Jmt</t>
+          <t>Höktjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>460157</v>
+        <v>460021</v>
       </c>
       <c r="R16" t="n">
-        <v>7077216</v>
+        <v>7077521</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2280,12 +2098,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2020-08-09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2020-08-09</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2300,62 +2118,60 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Tore Dahlberg, Karl Soler Kinnerbäck, Tove Lönneborg, Vera Ranow</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112769820</v>
+        <v>112769827</v>
       </c>
       <c r="B17" t="n">
-        <v>89897</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Svedbodarna Skärvången, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>460152</v>
+        <v>460299</v>
       </c>
       <c r="R17" t="n">
-        <v>7077440</v>
+        <v>7077377</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2390,12 +2206,18 @@
           <t>2023-10-16</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>rikligt</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2414,50 +2236,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>112769837</v>
+        <v>112769829</v>
       </c>
       <c r="B18" t="n">
-        <v>86197</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Svedbodarna Skärvången, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>459965</v>
+        <v>460154</v>
       </c>
       <c r="R18" t="n">
-        <v>7077442</v>
+        <v>7077489</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2492,12 +2312,18 @@
           <t>2023-10-16</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>rikligt</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2516,50 +2342,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112769814</v>
+        <v>112769830</v>
       </c>
       <c r="B19" t="n">
-        <v>56746</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Svedbodarna Skärvången, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>460015</v>
+        <v>460066</v>
       </c>
       <c r="R19" t="n">
-        <v>7077372</v>
+        <v>7077384</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2596,7 +2420,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2605,6 +2429,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2623,19 +2448,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>112769835</v>
+        <v>112769831</v>
       </c>
       <c r="B20" t="n">
-        <v>77981</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2666,10 +2486,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>460150</v>
+        <v>459774</v>
       </c>
       <c r="R20" t="n">
-        <v>7077286</v>
+        <v>7077615</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2734,19 +2554,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112769827</v>
+        <v>112769832</v>
       </c>
       <c r="B21" t="n">
-        <v>77981</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2777,10 +2592,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>460299</v>
+        <v>459796</v>
       </c>
       <c r="R21" t="n">
-        <v>7077377</v>
+        <v>7077506</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2845,50 +2660,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112769805</v>
+        <v>112769833</v>
       </c>
       <c r="B22" t="n">
-        <v>56746</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Svedbodarna Skärvången, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>460268</v>
+        <v>459986</v>
       </c>
       <c r="R22" t="n">
-        <v>7077413</v>
+        <v>7077406</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2925,7 +2738,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2934,6 +2747,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2952,50 +2766,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>112769813</v>
+        <v>112769834</v>
       </c>
       <c r="B23" t="n">
-        <v>56746</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Svedbodarna Skärvången, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>459963</v>
+        <v>460026</v>
       </c>
       <c r="R23" t="n">
-        <v>7077437</v>
+        <v>7077354</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3032,7 +2844,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3041,6 +2853,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3059,50 +2872,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>112769804</v>
+        <v>112769835</v>
       </c>
       <c r="B24" t="n">
-        <v>56746</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Svedbodarna Skärvången, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>460242</v>
+        <v>460150</v>
       </c>
       <c r="R24" t="n">
-        <v>7077229</v>
+        <v>7077286</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3139,7 +2950,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3148,6 +2959,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3166,50 +2978,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>112769816</v>
+        <v>112769836</v>
       </c>
       <c r="B25" t="n">
-        <v>56746</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Svedbodarna Skärvången, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>460123</v>
+        <v>460161</v>
       </c>
       <c r="R25" t="n">
-        <v>7077317</v>
+        <v>7077214</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3246,7 +3056,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3255,6 +3065,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3273,15 +3084,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>112769799</v>
+        <v>87490885</v>
       </c>
       <c r="B26" t="n">
-        <v>90583</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3289,37 +3095,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3298</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Svedbodarna Skärvången, Jmt</t>
+          <t>Höktjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>460132</v>
+        <v>460059</v>
       </c>
       <c r="R26" t="n">
-        <v>7077512</v>
+        <v>7077514</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3343,12 +3149,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2020-08-09</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2020-08-09</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3363,65 +3169,60 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Tore Dahlberg, Karl Soler Kinnerbäck, Tove Lönneborg, Vera Ranow</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>112769803</v>
+        <v>87490886</v>
       </c>
       <c r="B27" t="n">
-        <v>56746</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Svedbodarna Skärvången, Jmt</t>
+          <t>Höktjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>460371</v>
+        <v>460021</v>
       </c>
       <c r="R27" t="n">
-        <v>7077335</v>
+        <v>7077521</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3445,17 +3246,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2020-08-09</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2020-08-09</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3470,27 +3266,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Tore Dahlberg, Karl Soler Kinnerbäck, Tove Lönneborg, Vera Ranow</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>112769821</v>
+        <v>87485663</v>
       </c>
       <c r="B28" t="n">
-        <v>89919</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3498,37 +3289,45 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Svedbodarna Skärvången, Jmt</t>
+          <t>Höktjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>460268</v>
+        <v>459790</v>
       </c>
       <c r="R28" t="n">
-        <v>7077450</v>
+        <v>7077722</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3552,12 +3351,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2020-08-09</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2020-08-09</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3572,27 +3371,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Vera Ranow</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Vera Ranow, Tore Dahlberg, Karl Soler Kinnerbäck, Tove Lönneborg</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>112769822</v>
+        <v>112769803</v>
       </c>
       <c r="B29" t="n">
-        <v>89919</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3600,21 +3394,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3624,10 +3418,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>460082</v>
+        <v>460370</v>
       </c>
       <c r="R29" t="n">
-        <v>7077490</v>
+        <v>7077334</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3660,6 +3454,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2023-10-16</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3686,15 +3485,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>112769831</v>
+        <v>112769804</v>
       </c>
       <c r="B30" t="n">
-        <v>77981</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3702,37 +3496,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Svedbodarna Skärvången, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>459774</v>
+        <v>460242</v>
       </c>
       <c r="R30" t="n">
-        <v>7077615</v>
+        <v>7077229</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3769,7 +3560,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3778,7 +3569,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3797,15 +3587,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>112769834</v>
+        <v>112769805</v>
       </c>
       <c r="B31" t="n">
-        <v>77981</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3813,37 +3598,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Svedbodarna Skärvången, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>460026</v>
+        <v>460268</v>
       </c>
       <c r="R31" t="n">
-        <v>7077354</v>
+        <v>7077413</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3880,7 +3662,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3889,7 +3671,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3908,15 +3689,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>112769812</v>
+        <v>112769806</v>
       </c>
       <c r="B32" t="n">
-        <v>56746</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3948,10 +3724,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>459702</v>
+        <v>460220</v>
       </c>
       <c r="R32" t="n">
-        <v>7077612</v>
+        <v>7077367</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4015,15 +3791,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>112769825</v>
+        <v>112769807</v>
       </c>
       <c r="B33" t="n">
-        <v>89919</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4031,21 +3802,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4055,10 +3826,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>459944</v>
+        <v>459924</v>
       </c>
       <c r="R33" t="n">
-        <v>7077567</v>
+        <v>7077587</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4091,6 +3862,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2023-10-16</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4117,15 +3893,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>112769823</v>
+        <v>112769808</v>
       </c>
       <c r="B34" t="n">
-        <v>89919</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4133,21 +3904,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4157,10 +3928,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>459998</v>
+        <v>459886</v>
       </c>
       <c r="R34" t="n">
-        <v>7077493</v>
+        <v>7077602</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4193,6 +3964,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2023-10-16</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4219,15 +3995,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>112769833</v>
+        <v>112769809</v>
       </c>
       <c r="B35" t="n">
-        <v>77981</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4235,37 +4006,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Svedbodarna Skärvången, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>459985</v>
+        <v>459659</v>
       </c>
       <c r="R35" t="n">
-        <v>7077407</v>
+        <v>7077629</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4302,7 +4070,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4311,7 +4079,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4330,15 +4097,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>112769824</v>
+        <v>112769810</v>
       </c>
       <c r="B36" t="n">
-        <v>89919</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4346,21 +4108,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4370,10 +4132,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>459967</v>
+        <v>459659</v>
       </c>
       <c r="R36" t="n">
-        <v>7077537</v>
+        <v>7077627</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4406,6 +4168,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2023-10-16</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4432,15 +4199,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>112769832</v>
+        <v>112769811</v>
       </c>
       <c r="B37" t="n">
-        <v>77981</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4448,37 +4210,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Svedbodarna Skärvången, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>459796</v>
+        <v>459668</v>
       </c>
       <c r="R37" t="n">
-        <v>7077506</v>
+        <v>7077614</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4515,7 +4274,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4524,7 +4283,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4543,37 +4301,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>112769800</v>
+        <v>112769812</v>
       </c>
       <c r="B38" t="n">
-        <v>90583</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4583,10 +4336,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>459756</v>
+        <v>459702</v>
       </c>
       <c r="R38" t="n">
-        <v>7077610</v>
+        <v>7077612</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4619,6 +4372,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2023-10-16</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4645,15 +4403,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>112769818</v>
+        <v>112769813</v>
       </c>
       <c r="B39" t="n">
-        <v>56746</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4685,10 +4438,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>460180</v>
+        <v>459963</v>
       </c>
       <c r="R39" t="n">
-        <v>7077236</v>
+        <v>7077438</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4725,7 +4478,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4752,15 +4505,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>112769809</v>
+        <v>112769814</v>
       </c>
       <c r="B40" t="n">
-        <v>56746</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4792,10 +4540,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>459659</v>
+        <v>460015</v>
       </c>
       <c r="R40" t="n">
-        <v>7077629</v>
+        <v>7077372</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4859,37 +4607,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>112769798</v>
+        <v>112769815</v>
       </c>
       <c r="B41" t="n">
-        <v>90583</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4899,10 +4642,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>460168</v>
+        <v>460116</v>
       </c>
       <c r="R41" t="n">
-        <v>7077479</v>
+        <v>7077317</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4937,6 +4680,11 @@
           <t>2023-10-16</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -4958,6 +4706,307 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>112769816</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Svedbodarna Skärvången, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>460122</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7077318</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2023-10-16</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2023-10-16</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>112769818</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Svedbodarna Skärvången, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>460180</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7077236</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2023-10-16</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2023-10-16</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>87490908</v>
+      </c>
+      <c r="B44" t="n">
+        <v>80398</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Höktjärnbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>460030</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7077510</v>
+      </c>
+      <c r="S44" t="n">
+        <v>20</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2020-08-09</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2020-08-09</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg, Karl Soler Kinnerbäck, Tove Lönneborg, Vera Ranow</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43541-2023 artfynd.xlsx
+++ b/artfynd/A 43541-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AZ44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112769837</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490895</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490896</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112769820</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490875</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490876</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87485661</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112769798</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112769799</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112769800</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112769801</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112769802</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87487081</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490916</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490917</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2233,6 +2313,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112769827</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2339,6 +2424,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112769829</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2445,6 +2535,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112769830</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2551,6 +2646,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112769831</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2657,6 +2757,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112769832</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2763,6 +2868,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112769833</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2869,6 +2979,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112769834</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2975,6 +3090,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112769835</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3081,6 +3201,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112769836</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3178,6 +3303,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490885</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3275,6 +3405,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490886</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3380,6 +3515,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87485663</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3482,6 +3622,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112769803</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3584,6 +3729,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112769804</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3686,6 +3836,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112769805</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3788,6 +3943,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112769806</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3890,6 +4050,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112769807</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3992,6 +4157,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112769808</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4094,6 +4264,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112769809</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4196,6 +4371,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112769810</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4298,6 +4478,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112769811</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4400,6 +4585,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112769812</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4502,6 +4692,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112769813</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4604,6 +4799,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112769814</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4706,6 +4906,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112769815</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4808,6 +5013,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112769816</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4910,6 +5120,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112769818</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5007,8 +5222,58 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490908</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>